--- a/Packages/cn.etetet.twsmap/Luban/Config/Datas/Chapter.xlsx
+++ b/Packages/cn.etetet.twsmap/Luban/Config/Datas/Chapter.xlsx
@@ -81,7 +81,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +98,13 @@
     </font>
     <font>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -571,141 +578,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1032,7 +1046,7 @@
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="30.125" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
@@ -1080,34 +1094,34 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="2:3">
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:3">
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:3">
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
